--- a/AI云业务/客户结算/hehe云业务消耗费用.xlsx
+++ b/AI云业务/客户结算/hehe云业务消耗费用.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="华为云" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="华为云_202608" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="华为云_202607" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="华为云_202609" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -483,32 +484,37 @@
           <t>账号信息</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>实际消耗（￥）</t>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>币种</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>实际消耗（原币）</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>服务费比例</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>服务费金额（￥）</t>
-        </is>
-      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>结算总金额（￥）</t>
+          <t>服务费金额（原币）</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>结算总金额（原币）</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>服务费是否支付</t>
         </is>
@@ -530,26 +536,31 @@
           <t>主账号</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>16802.07</v>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>336.04</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>17138.11</v>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
       </c>
-      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -567,26 +578,31 @@
           <t>程序化账号</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>115218.86</v>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>2304.38</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>117523.24</v>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
       </c>
-      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -604,26 +620,31 @@
           <t>网盟账号</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>96793.2</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1935.86</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>98729.06</v>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n"/>
+      <c r="J5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -641,102 +662,121 @@
           <t>hehe</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>935183.01</v>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>935183.01</v>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
       </c>
-      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>202608</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>华为云</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>主账号</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>20790.23</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>415.8</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>21206.03</v>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>真实消耗已预充值</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n"/>
+          <t>hehe</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>47082.98</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>47082.98</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值（无服务费）</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>202608</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>华为云</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>程序化账号</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>332065.38</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>6641.31</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>338706.69</v>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>真实消耗已预充值</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n"/>
+          <t>王杰</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>8104.49</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>8104.49</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值（无服务费）</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -751,29 +791,34 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>网盟账号</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>96979.55</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+          <t>主账号</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>20790.23</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>1939.59</v>
-      </c>
       <c r="G9" s="4" t="n">
-        <v>98919.14</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
+        <v>415.8</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>21206.03</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
       </c>
-      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -783,36 +828,39 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>阿里云</t>
+          <t>腾讯云</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>hehe</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1048829.13</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
+          <t>程序化账号</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>332065.38</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1048829.13</v>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>真实消耗已预充值（无服务费）</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n"/>
+        <v>6641.31</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>338706.69</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -822,110 +870,127 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>华为云</t>
+          <t>腾讯云</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>hehe</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>58632.05</v>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
+          <t>网盟账号</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>96979.55</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G11" s="4" t="n">
-        <v>58632.05</v>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>真实消耗已预充值（无服务费）</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n"/>
+        <v>1939.59</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>98919.14</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>阿里云</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>主账号</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>17247.24</v>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>344.94</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>17592.18</v>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>真实消耗已预充值</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
+          <t>hehe</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1048829.13</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1048829.13</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值（无服务费）</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>华为云</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>程序化账号</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>356787.53</v>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>7135.75</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>363923.28</v>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>真实消耗已预充值</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n"/>
+          <t>hehe</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>58632.05</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>58632.05</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值（无服务费）</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -940,29 +1005,34 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>网盟账号</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>97085.84</v>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
+          <t>主账号</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>17247.24</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>1941.72</v>
-      </c>
       <c r="G14" s="4" t="n">
-        <v>99027.56</v>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
+        <v>344.94</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>17592.18</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>真实消耗已预充值</t>
         </is>
       </c>
-      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -972,36 +1042,39 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>阿里云</t>
+          <t>腾讯云</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>hehe</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>1142378.06</v>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
+          <t>程序化账号</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>356787.53</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1142378.06</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>真实消耗已预充值（无服务费）</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
+        <v>7135.75</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>363923.28</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1011,57 +1084,148 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>华为云</t>
+          <t>腾讯云</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>hehe</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>58067.91</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
+          <t>网盟账号</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>97085.84</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>58067.91</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>真实消耗已预充值（无服务费）</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="n"/>
+        <v>1941.72</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>99027.56</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>阿里云</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>hehe</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>1142378.06</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1142378.06</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值（无服务费）</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>华为云</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>hehe</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>58067.91</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>58067.91</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值（无服务费）</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="4" t="n">
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="E19" s="4" t="n">
         <v>4392860.06</v>
       </c>
-      <c r="E17" s="3" t="n"/>
-      <c r="F17" s="4" t="n">
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="4" t="n">
         <v>22995.39</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>4415855.45</v>
       </c>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1149,13 +1313,114 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>华为云</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>业务所属期</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>账号信息</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>实际消耗（￥）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>hehe</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>47082.98</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值（无服务费）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王杰</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8104.49</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值（无服务费）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="4" t="n">
+        <v>55187.47</v>
+      </c>
+      <c r="D5" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1252,22 +1517,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>202608</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>腾讯云</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>449835.16</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>8996.700000000001</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>458831.86</v>
+          <t>华为云</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>55187.47</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>55187.47</v>
       </c>
     </row>
     <row r="8">
@@ -1278,17 +1543,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>阿里云</t>
+          <t>腾讯云</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1048829.13</v>
+        <v>449835.16</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0</v>
+        <v>8996.700000000001</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>1048829.13</v>
+        <v>458831.86</v>
       </c>
     </row>
     <row r="9">
@@ -1299,38 +1564,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>华为云</t>
+          <t>阿里云</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>58632.05</v>
+        <v>1048829.13</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>58632.05</v>
+        <v>1048829.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>腾讯云</t>
+          <t>华为云</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>471120.61</v>
+        <v>58632.05</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>9422.41</v>
+        <v>0</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>480543.02</v>
+        <v>58632.05</v>
       </c>
     </row>
     <row r="11">
@@ -1341,17 +1606,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>阿里云</t>
+          <t>腾讯云</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1142378.06</v>
+        <v>471120.61</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>9422.41</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1142378.06</v>
+        <v>480543.02</v>
       </c>
     </row>
     <row r="12">
@@ -1362,111 +1627,132 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>华为云</t>
+          <t>阿里云</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>58067.91</v>
+        <v>1142378.06</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="6" t="n">
+        <v>1142378.06</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>华为云</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
         <v>58067.91</v>
       </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>58067.91</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>二、每月总消耗（全云合计）</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>业务所属期</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>实际消耗合计（￥）</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>服务费合计（￥）</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>结算合计（￥）</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>202609</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>1163997.14</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>4576.28</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>1168573.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>202608</t>
+          <t>202609</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>1557296.34</v>
+        <v>1219184.61</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>8996.700000000001</v>
+        <v>4576.28</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1566293.04</v>
+        <v>1223760.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>202608</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>1671566.58</v>
+        <v>1557296.34</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>9422.41</v>
+        <v>8996.700000000001</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1680988.99</v>
+        <v>1566293.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>1671566.58</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>9422.41</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1680988.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>全部期间合计</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>4392860.06</v>
-      </c>
-      <c r="C19" s="6" t="n">
+      <c r="B20" s="6" t="n">
+        <v>4448047.53</v>
+      </c>
+      <c r="C20" s="6" t="n">
         <v>22995.39</v>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>4415855.45</v>
+      <c r="D20" s="6" t="n">
+        <v>4471042.92</v>
       </c>
     </row>
   </sheetData>
@@ -1662,7 +1948,6 @@
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="3" t="n"/>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
@@ -1783,7 +2068,6 @@
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="3" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -2615,7 +2899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2654,40 +2938,40 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>202608</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>hehe</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>58632.05</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>47082.98</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>202607</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>hehe</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>58067.91</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>202609</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>王杰</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8104.49</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>真实消耗已预充值（无服务费）</t>
         </is>
@@ -2696,14 +2980,54 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>202608</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>hehe</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>58632.05</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值（无服务费）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>202607</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>hehe</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>58067.91</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>真实消耗已预充值（无服务费）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="4" t="n">
-        <v>116699.96</v>
-      </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="4" t="n">
+        <v>171887.43</v>
+      </c>
+      <c r="D7" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
